--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -905,22 +905,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -944,19 +944,19 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -982,22 +982,22 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1018,7 +1018,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1030,10 +1030,10 @@
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1059,22 +1059,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1098,10 +1098,10 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1136,22 +1136,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1172,10 +1172,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1184,10 +1184,10 @@
         <v>-1</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1213,22 +1213,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1252,10 +1252,10 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>-1</v>
@@ -1264,7 +1264,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1290,22 +1290,22 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1338,10 +1338,10 @@
         <v>-1</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1367,22 +1367,22 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1406,7 +1406,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1415,10 +1415,10 @@
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1444,22 +1444,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1483,10 +1483,10 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>-1</v>
@@ -1521,22 +1521,22 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1560,10 +1560,10 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1598,22 +1598,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1634,10 +1634,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1649,7 +1649,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1675,22 +1675,22 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1714,7 +1714,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1752,10 +1752,10 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1764,10 +1764,10 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1788,7 +1788,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1803,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1829,22 +1829,22 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1868,10 +1868,10 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>-1</v>
@@ -1906,22 +1906,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1942,13 +1942,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1983,22 +1983,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2022,10 +2022,10 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2060,22 +2060,22 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2096,10 +2096,10 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2108,7 +2108,7 @@
         <v>-1</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2137,22 +2137,22 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2176,10 +2176,10 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2214,22 +2214,22 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2253,19 +2253,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>-1</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2291,22 +2291,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2368,22 +2368,22 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2404,10 +2404,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2445,22 +2445,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2487,7 +2487,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>-1</v>
@@ -2522,22 +2522,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2558,10 +2558,10 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2570,10 +2570,10 @@
         <v>-1</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2599,22 +2599,22 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2635,7 +2635,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2650,7 +2650,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2676,22 +2676,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2712,10 +2712,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2727,7 +2727,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2753,22 +2753,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2830,22 +2830,22 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2866,10 +2866,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2881,7 +2881,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2895,10 +2895,10 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2907,7 +2907,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3007,19 +3007,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>65.38</v>
       </c>
       <c r="G3">
-        <v>46.15</v>
+        <v>30.77</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -3039,19 +3039,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="G4">
-        <v>30.77</v>
+        <v>19.23</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4107,7 +4107,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4139,16 +4139,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920202</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
         <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4162,16 +4162,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920202</v>
+        <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
         <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4185,16 +4185,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920204</v>
+        <v>20330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4208,16 +4208,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920204</v>
+        <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4231,62 +4231,62 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920213</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920213</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920214</v>
+        <v>20330051920213</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4300,16 +4300,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920214</v>
+        <v>20330051920213</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4323,16 +4323,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920192</v>
+        <v>20330051920214</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4346,16 +4346,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920197</v>
+        <v>20330051920214</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4369,39 +4369,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920198</v>
+        <v>20330051920218</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920199</v>
+        <v>20330051920218</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4415,16 +4415,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920201</v>
+        <v>20330051920191</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4438,16 +4438,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920290</v>
+        <v>20330051920197</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4461,16 +4461,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920210</v>
+        <v>20330051920198</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4484,16 +4484,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920215</v>
+        <v>20330051920199</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4507,16 +4507,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920217</v>
+        <v>20330051920201</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4525,6 +4525,121 @@
         <v>48</v>
       </c>
       <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920202</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920290</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920210</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920215</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920217</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1915,7 +1915,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -1992,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2146,7 +2146,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2300,7 +2300,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2336,7 +2336,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2762,7 +2762,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2798,7 +2798,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>20</v>

--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -200,6 +200,9 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -218,18 +221,30 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -239,15 +254,24 @@
     <t>DE LA TEJA</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
@@ -263,7 +287,7 @@
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>TREJO</t>
   </si>
   <si>
     <t>OLIVERA</t>
@@ -272,6 +296,12 @@
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
@@ -287,7 +317,10 @@
     <t>SOLIS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>REYNA ARISBETH</t>
@@ -296,6 +329,9 @@
     <t>ANALI</t>
   </si>
   <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
     <t>DULCE FERNANDA</t>
   </si>
   <si>
@@ -317,18 +353,30 @@
     <t>YAMILET</t>
   </si>
   <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
     <t>ITZEL</t>
   </si>
   <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
+    <t>MARITZA JULIANA</t>
+  </si>
+  <si>
     <t>HEIDY MARIAM</t>
   </si>
   <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
     <t>JULIO CESAR</t>
   </si>
   <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
     <t>SUSANA</t>
   </si>
   <si>
@@ -347,58 +395,10 @@
     <t>ALISSON FERNANDA</t>
   </si>
   <si>
+    <t>EMILY</t>
+  </si>
+  <si>
     <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>EMILY</t>
   </si>
   <si>
     <t>MARLENE</t>
@@ -896,7 +896,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -914,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -950,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -973,7 +973,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -991,7 +991,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -1027,7 +1027,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1127,7 +1127,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1145,7 +1145,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1204,7 +1204,7 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1222,7 +1222,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1258,7 +1258,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1281,7 +1281,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -1299,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1376,7 +1376,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1435,7 +1435,7 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1489,7 +1489,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1512,7 +1512,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1566,7 +1566,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1589,7 +1589,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1607,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1643,7 +1643,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1666,7 +1666,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -1684,7 +1684,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1720,7 +1720,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1740,10 +1740,10 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1758,10 +1758,10 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -1794,10 +1794,10 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1820,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1838,7 +1838,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1874,7 +1874,7 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -2051,7 +2051,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -2069,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2105,7 +2105,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2205,7 +2205,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2223,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -2259,7 +2259,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2359,7 +2359,7 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -2377,7 +2377,7 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2413,7 +2413,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2436,7 +2436,7 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2490,7 +2490,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2513,7 +2513,7 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -2567,7 +2567,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2590,7 +2590,7 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -2608,7 +2608,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -2644,7 +2644,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2667,7 +2667,7 @@
         <v>7</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>8</v>
@@ -2685,7 +2685,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -2721,7 +2721,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2821,7 +2821,7 @@
         <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -2839,7 +2839,7 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -2875,7 +2875,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -2975,25 +2975,25 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>23.08</v>
+        <v>61.54</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>38.46</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>76.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3010,22 +3010,22 @@
         <v>17</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>65.38</v>
       </c>
       <c r="G3">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3163,7 +3163,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3188,426 +3188,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920190</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920191</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920193</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920196</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920197</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920198</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920199</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920200</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920200</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920201</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920202</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920204</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920290</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920210</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920213</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920214</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920215</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920177</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920217</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920218</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920259</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3643,53 +3223,53 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920200</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920192</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3697,16 +3277,16 @@
         <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3714,16 +3294,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3731,16 +3311,16 @@
         <v>20330051920197</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3748,16 +3328,16 @@
         <v>20330051920198</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3765,231 +3345,231 @@
         <v>20330051920199</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920201</v>
+        <v>20330051920200</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920202</v>
+        <v>20330051920201</v>
       </c>
       <c r="B11" t="s">
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920204</v>
+        <v>19330051920280</v>
       </c>
       <c r="B12" t="s">
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920290</v>
+        <v>20330051920202</v>
       </c>
       <c r="B13" t="s">
         <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920210</v>
+        <v>20330051920204</v>
       </c>
       <c r="B14" t="s">
         <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920213</v>
+        <v>20330051920206</v>
       </c>
       <c r="B15" t="s">
         <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920214</v>
+        <v>19330051920290</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920215</v>
+        <v>20330051920209</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920177</v>
+        <v>20330051920210</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920217</v>
+        <v>20330051920212</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920218</v>
+        <v>20330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920259</v>
+        <v>20330051920214</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920192</v>
+        <v>20330051920215</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
         <v>121</v>
@@ -4000,13 +3580,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920280</v>
+        <v>19330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
         <v>122</v>
@@ -4017,13 +3597,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920206</v>
+        <v>20330051920217</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
         <v>123</v>
@@ -4034,13 +3614,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920209</v>
+        <v>20330051920218</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>124</v>
@@ -4051,13 +3631,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920212</v>
+        <v>20330051920219</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
         <v>125</v>
@@ -4068,13 +3648,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920219</v>
+        <v>20330051920259</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
         <v>126</v>
@@ -4088,10 +3668,10 @@
         <v>19330051920183</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
         <v>127</v>
@@ -4107,7 +3687,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4145,10 +3725,10 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4168,10 +3748,10 @@
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4180,27 +3760,27 @@
         <v>48</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920193</v>
+        <v>20330051920196</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4208,68 +3788,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920193</v>
+        <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920214</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4277,22 +3857,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920213</v>
+        <v>20330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4300,45 +3880,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920213</v>
+        <v>20330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920214</v>
+        <v>20330051920198</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4346,45 +3926,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920214</v>
+        <v>20330051920213</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920218</v>
+        <v>20330051920217</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4395,252 +3975,22 @@
         <v>20330051920218</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920191</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920197</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920198</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920199</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920201</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920202</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920290</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920210</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920215</v>
-      </c>
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920217</v>
-      </c>
-      <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -932,7 +932,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1009,7 +1009,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1086,7 +1086,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1163,7 +1163,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1181,7 +1181,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1240,7 +1240,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1317,7 +1317,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1394,7 +1394,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1412,7 +1412,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1548,7 +1548,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1625,7 +1625,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1702,7 +1702,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1779,7 +1779,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1856,7 +1856,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1933,7 +1933,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2010,7 +2010,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2028,7 +2028,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2087,7 +2087,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2105,7 +2105,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2164,7 +2164,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2241,7 +2241,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2318,7 +2318,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2395,7 +2395,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2472,7 +2472,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2549,7 +2549,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2626,7 +2626,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2703,7 +2703,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2780,7 +2780,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2857,7 +2857,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2975,19 +2975,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>61.54</v>
+        <v>53.85</v>
       </c>
       <c r="G2">
-        <v>38.46</v>
+        <v>46.15</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3687,7 +3687,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3765,22 +3765,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920196</v>
+        <v>20330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3788,22 +3788,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920196</v>
+        <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3811,22 +3811,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920214</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3834,22 +3834,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920214</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920191</v>
+        <v>20330051920214</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3880,22 +3880,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920193</v>
+        <v>20330051920214</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920198</v>
+        <v>20330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3926,22 +3926,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920213</v>
+        <v>20330051920218</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3949,16 +3949,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920217</v>
+        <v>20330051920191</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -3972,24 +3972,70 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920218</v>
+        <v>20330051920198</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920213</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
         <v>49</v>
       </c>
-      <c r="G13">
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920217</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -938,7 +938,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1015,7 +1015,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -1092,7 +1092,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1169,7 +1169,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1246,7 +1246,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1323,7 +1323,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1341,7 +1341,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1400,7 +1400,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1418,7 +1418,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1477,7 +1477,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1554,7 +1554,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1572,7 +1572,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1631,7 +1631,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1708,7 +1708,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1785,7 +1785,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1803,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1862,7 +1862,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1939,7 +1939,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1957,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2016,7 +2016,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2093,7 +2093,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2170,7 +2170,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2247,7 +2247,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2324,7 +2324,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2401,7 +2401,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2496,7 +2496,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2555,7 +2555,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2632,7 +2632,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2786,7 +2786,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2804,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2863,7 +2863,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2881,7 +2881,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2904,7 +2904,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -167,10 +167,10 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -926,10 +926,10 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -944,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1003,10 +1003,10 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -1024,7 +1024,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1080,10 +1080,10 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1157,10 +1157,10 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -1175,10 +1175,10 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1234,10 +1234,10 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>7</v>
@@ -1311,10 +1311,10 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>6</v>
@@ -1329,7 +1329,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1388,10 +1388,10 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -1406,7 +1406,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1465,10 +1465,10 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1542,10 +1542,10 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -1560,10 +1560,10 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1619,10 +1619,10 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1640,7 +1640,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1696,10 +1696,10 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1717,7 +1717,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1773,10 +1773,10 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>4</v>
@@ -1791,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1850,10 +1850,10 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1927,10 +1927,10 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -2004,10 +2004,10 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2081,10 +2081,10 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -2099,7 +2099,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2158,10 +2158,10 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2235,10 +2235,10 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>7</v>
@@ -2312,10 +2312,10 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2389,10 +2389,10 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>6</v>
@@ -2410,7 +2410,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2466,10 +2466,10 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2484,10 +2484,10 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2543,10 +2543,10 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -2561,10 +2561,10 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2620,10 +2620,10 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>5</v>
@@ -2641,7 +2641,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2697,10 +2697,10 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>4</v>
@@ -2718,7 +2718,7 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2774,10 +2774,10 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2851,10 +2851,10 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>4</v>
@@ -2869,10 +2869,10 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3007,19 +3007,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>65.38</v>
+        <v>80.77</v>
       </c>
       <c r="G3">
-        <v>34.62</v>
+        <v>19.23</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3039,19 +3039,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="G4">
-        <v>19.23</v>
+        <v>15.38</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3687,7 +3687,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>19330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>19330051920177</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3765,22 +3765,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920193</v>
+        <v>20330051920218</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3788,16 +3788,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920193</v>
+        <v>20330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -3811,16 +3811,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920259</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -3834,22 +3834,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920259</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920214</v>
+        <v>20330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3880,16 +3880,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920214</v>
+        <v>20330051920191</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -3903,22 +3903,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920218</v>
+        <v>20330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3926,16 +3926,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920218</v>
+        <v>20330051920198</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -3949,16 +3949,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920191</v>
+        <v>20330051920214</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920198</v>
+        <v>20330051920217</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -3990,52 +3990,6 @@
         <v>48</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920213</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920217</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -923,7 +923,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -1000,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -1077,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1095,7 +1095,7 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1154,7 +1154,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1308,7 +1308,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1385,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -1403,7 +1403,7 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1462,7 +1462,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1539,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1616,7 +1616,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1770,7 +1770,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1847,7 +1847,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2001,7 +2001,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -2078,7 +2078,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -2096,7 +2096,7 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2155,7 +2155,7 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -2232,7 +2232,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -2309,7 +2309,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2386,7 +2386,7 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2463,7 +2463,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>8</v>
@@ -2540,7 +2540,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2617,7 +2617,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>7</v>
@@ -2694,7 +2694,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -2712,7 +2712,7 @@
         <v>7</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2771,7 +2771,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -2848,7 +2848,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -2866,7 +2866,7 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2901,7 +2901,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ALCV - Estadisticos 20221.xlsx
+++ b/grupos/5ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="128">
   <si>
     <t>Materia</t>
   </si>
@@ -167,10 +167,10 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -935,7 +935,7 @@
         <v>4</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -1012,7 +1012,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>6</v>
@@ -1089,7 +1089,7 @@
         <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1107,7 +1107,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1166,7 +1166,7 @@
         <v>4</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -1243,7 +1243,7 @@
         <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1320,7 +1320,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1338,7 +1338,7 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1397,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1415,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -1551,7 +1551,7 @@
         <v>4</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -1569,7 +1569,7 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1628,7 +1628,7 @@
         <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1705,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1782,7 +1782,7 @@
         <v>4</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>6</v>
@@ -1800,7 +1800,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1859,7 +1859,7 @@
         <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>9</v>
@@ -1936,7 +1936,7 @@
         <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -2013,7 +2013,7 @@
         <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -2090,7 +2090,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -2167,7 +2167,7 @@
         <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -2244,7 +2244,7 @@
         <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2321,7 +2321,7 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -2398,7 +2398,7 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>9</v>
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2552,7 +2552,7 @@
         <v>4</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -2629,7 +2629,7 @@
         <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>6</v>
@@ -2647,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2706,7 +2706,7 @@
         <v>4</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>7</v>
@@ -2783,7 +2783,7 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>9</v>
@@ -2801,7 +2801,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2860,7 +2860,7 @@
         <v>4</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>6</v>
@@ -2878,7 +2878,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3007,19 +3007,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="G3">
-        <v>19.23</v>
+        <v>15.38</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3039,19 +3039,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>84.62</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>15.38</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3687,7 +3687,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920177</v>
+        <v>20330051920196</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920177</v>
+        <v>20330051920196</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3765,22 +3765,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920218</v>
+        <v>20330051920200</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3788,16 +3788,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920218</v>
+        <v>20330051920200</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -3811,22 +3811,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920259</v>
+        <v>20330051920204</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3834,22 +3834,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920259</v>
+        <v>20330051920204</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920190</v>
+        <v>20330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3880,16 +3880,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920191</v>
+        <v>20330051920218</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -3903,16 +3903,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920193</v>
+        <v>20330051920190</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -3926,16 +3926,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920198</v>
+        <v>20330051920191</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -3949,16 +3949,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920214</v>
+        <v>20330051920193</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920217</v>
+        <v>20330051920198</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -3990,6 +3990,98 @@
         <v>48</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920214</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920177</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920217</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920259</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>
